--- a/stories/arbres/TREE-FAM-005.xlsx
+++ b/stories/arbres/TREE-FAM-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est au parc, avec maman. Papa arrive bientôt. Léa sent un malaise. Son ventre est serré. Elle a un peu peur. Maman dit : si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Léa est au parc, avec maman. Papa arrive bientôt. Léa sent un malaise. Son ventre est serré. Elle a un peu peur. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est au parc, avec maman. Papa arrive bientôt. Léa sent un malaise. Son ventre est serré. Elle a un peu peur.
+maman|Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1514,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1543,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa joue avec Tom. Tom dit : c'est un secret. Léa sent un malaise. Elle a peur. Elle va vers maman. Elle raconte à maman. On raconte à papa ou maman.</t>
+          <t>Léa joue avec Tom. C'est un secret. Léa sent un malaise. Elle a peur. Elle va vers maman. Elle raconte à maman. On raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1681,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa joue avec Tom.
+enfant-m|C'est un secret.
+narrateur|Léa sent un malaise. Elle a peur. Elle va vers maman. Elle raconte à maman. On raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Un malaise, on raconte à papa ou maman ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Léa respire. Maman est là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2228,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2395,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et Tom ont les cubes. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa. Maman montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2586,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2753,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi Tom. Puis les cubes. Puis une pomme. On souffle doucement. Léa marche près de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2920,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2879,7 +2949,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Léa s'arrête près de un yaourt. les cubes est rangé. On attend son tour. Léa dit : j'ai appris. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+          <t>Léa s'arrête près de un yaourt. les cubes est rangé. On attend son tour. J'ai appris. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3017,6 +3087,13 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête près de un yaourt. les cubes est rangé. On attend son tour.
+enfant-f|J'ai appris. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman.
+narrateur|Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se souvient de Tom. Et de les cubes. Et de un morceau de pain. On entend un oiseau. Léa écoute maman encore une fois. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3619,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Léa et Tom ont le livre. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa. Maman dit : je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Léa et Tom ont le livre. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa. Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3757,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et Tom ont le livre. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa.
+maman|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3949,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4116,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Léa s'arrête. Le savon sent bon. Léa pose sa tête un moment. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4283,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4450,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa range le livre. un yaourt reste près de Tom. Il y a des miettes sur la table. Léa souffle, puis sourit à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4617,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4646,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. L'eau coule, tout petit bruit. Léa montre un morceau de pain à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+          <t>Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. L'eau coule, tout petit bruit. Léa montre un morceau de pain à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4784,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. L'eau coule, tout petit bruit. Léa montre un morceau de pain à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4951,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5118,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et Tom ont la dînette. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa. Maman reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5309,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5476,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une pomme. la dînette est rangé. Tom est fini. Un linge sèche à l'air. Léa range encore un peu, près de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5643,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5810,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Léa pose la dînette. Tom est derrière. Un chat miaule une fois. Léa range la tasse. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5977,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6144,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa montre un morceau de pain. Maman a vu Tom. Et la dînette. Un ballon s'immobilise. Léa chuchote : c'est fini. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6311,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6340,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa joue avec une amie Léa. L'amie dit : ne dis rien. Léa a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à maman. Plus tard, elle le dira à papa.</t>
+          <t>Léa joue avec une amie Léa. Ne dis rien. Léa a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à maman. Plus tard, elle le dira à papa.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6478,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa joue avec une amie Léa.
+enfant-f|Ne dis rien.
+narrateur|Léa a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à maman. Plus tard, elle le dira à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6665,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Si on a peur, on fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6838,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Léa retient le geste. Maman sourit. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7029,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7058,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa et son amie ont les cubes. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute. Maman dit : je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Léa et son amie ont les cubes. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute. Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7196,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et son amie ont les cubes. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute.
+maman|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7388,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7555,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi Léa. Puis les cubes. Puis une pomme. Le vent est doux. Léa plie un pull. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7722,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7889,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête près de un yaourt. les cubes est rangé. Une chaussette est encore sablée. Léa s'assoit près de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8056,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8223,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se souvient de Léa. Et de les cubes. Et de un morceau de pain. La lumière est claire. Léa sourit. Maman sourit aussi. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8390,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8557,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et son amie ont le livre. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute. Maman reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8748,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8915,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Léa s'arrête. Un panier est posé sur le banc. Léa dit merci à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9082,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9249,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa range le livre. un yaourt reste près de Léa. On range un objet. Léa prend la main de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9416,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9445,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On se tient la main. Léa pose le livre à sa place. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+          <t>Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On se tient la main. Léa pose le livre à sa place. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9583,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On se tient la main. Léa pose le livre à sa place. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9750,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9917,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et son amie ont la dînette. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute. Maman montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10108,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10275,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une pomme. la dînette est rangé. Léa est fini. Une tasse cliquette. Léa tend une pomme à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10442,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10609,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Léa pose la dînette. Léa est derrière. Une cloche tinte, tout loin. Papa n'est pas loin. Léa les rejoint. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10776,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10943,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa montre un morceau de pain. Maman a vu Léa. Et la dînette. On écoute jusqu'au bout. Léa enfile ses chaussons. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11110,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11277,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa joue avec Sami. Un bruit étrange vient du bois. Léa a peur. Elle sent un malaise. Elle raconte à maman. Maman l'écoute. On raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On garde le malaise, ou on raconte ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Léa hoche la tête. On continue, avec maman. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11491,6 +11822,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11653,6 +11989,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et Sami ont les cubes. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman. Maman reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12180,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12001,6 +12347,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi Sami. Puis les cubes. Puis une pomme. Une pomme brille un peu. Léa caresse le doudou. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12514,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12681,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête près de un yaourt. les cubes est rangé. Ça sent le pain chaud. Léa serre la main de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se souvient de Sami. Et de les cubes. Et de un morceau de pain. Un ruban reste dans la poche. Léa essuie ses mains. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13182,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13349,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et Sami ont le livre. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman. Maman montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13540,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13321,6 +13707,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Léa s'arrête. Une feuille tombe. Léa range Sami dans sa tête, comme un souvenir. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13874,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14041,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa range le livre. un yaourt reste près de Sami. Un vélo passe au loin. Léa ferme le sac. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14208,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13831,7 +14237,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Les chaussures font toc toc. Léa répète tout bas le geste. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+          <t>Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Les chaussures font toc toc. Léa répète tout bas le geste. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13969,6 +14375,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Les chaussures font toc toc. Léa répète tout bas le geste. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14542,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14155,7 +14571,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Léa et Sami ont la dînette. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman. Maman dit : je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Léa et Sami ont la dînette. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman. Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14293,6 +14709,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa et Sami ont la dînette. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman.
+maman|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14901,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15068,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint une pomme. la dînette est rangé. Sami est fini. La couverture est douce. Léa raccroche un linge. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15235,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15402,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Léa pose la dînette. Sami est derrière. Le sol est un peu froid. Léa boit une gorgée d'eau. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15569,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15736,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa montre un morceau de pain. Maman a vu Sami. Et la dînette. Un galet est encore chaud. Léa ferme la porte, tout doux. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15903,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15486,6 +15943,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-005.xlsx
+++ b/stories/arbres/TREE-FAM-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,11 @@
 maman|Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1519,6 +1529,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1688,6 +1699,7 @@
 narrateur|Léa sent un malaise. Elle a peur. Elle va vers maman. Elle raconte à maman. On raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1883,7 @@
           <t>narrateur|Un malaise, on raconte à papa ou maman ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2055,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Léa respire. Maman est là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2233,6 +2247,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2400,6 +2415,7 @@
           <t>narrateur|Léa et Tom ont les cubes. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa. Maman montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2591,6 +2607,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2758,6 +2775,7 @@
           <t>narrateur|Léa a choisi Tom. Puis les cubes. Puis une pomme. On souffle doucement. Léa marche près de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2925,6 +2943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3113,7 @@
 narrateur|Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3449,7 @@
           <t>narrateur|Léa se souvient de Tom. Et de les cubes. Et de un morceau de pain. On entend un oiseau. Léa écoute maman encore une fois. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3763,6 +3786,7 @@
 maman|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3978,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4121,6 +4146,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Léa s'arrête. Le savon sent bon. Léa pose sa tête un moment. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4288,6 +4314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4455,6 +4482,7 @@
           <t>narrateur|Léa range le livre. un yaourt reste près de Tom. Il y a des miettes sur la table. Léa souffle, puis sourit à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4622,6 +4650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4789,6 +4818,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. L'eau coule, tout petit bruit. Léa montre un morceau de pain à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4956,6 +4986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5123,6 +5154,7 @@
           <t>narrateur|Léa et Tom ont la dînette. Le malaise est encore là. Léa a peur. Elle raconte à maman. Elle racontera à papa. Maman reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5314,6 +5346,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5481,6 +5514,7 @@
           <t>narrateur|Léa rejoint une pomme. la dînette est rangé. Tom est fini. Un linge sèche à l'air. Léa range encore un peu, près de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5648,6 +5682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5815,6 +5850,7 @@
           <t>narrateur|Près de un yaourt. Léa pose la dînette. Tom est derrière. Un chat miaule une fois. Léa range la tasse. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5982,6 +6018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6149,6 +6186,7 @@
           <t>narrateur|Léa montre un morceau de pain. Maman a vu Tom. Et la dînette. Un ballon s'immobilise. Léa chuchote : c'est fini. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6316,6 +6354,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6524,7 @@
 narrateur|Léa a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à maman. Plus tard, elle le dira à papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6672,6 +6712,7 @@
           <t>narrateur|Si on a peur, on fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6843,6 +6884,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Léa retient le geste. Maman sourit. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7034,6 +7076,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7202,6 +7245,7 @@
 maman|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7393,6 +7437,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7560,6 +7605,7 @@
           <t>narrateur|Léa a choisi Léa. Puis les cubes. Puis une pomme. Le vent est doux. Léa plie un pull. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7727,6 +7773,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7894,6 +7941,7 @@
           <t>narrateur|Léa s'arrête près de un yaourt. les cubes est rangé. Une chaussette est encore sablée. Léa s'assoit près de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8061,6 +8109,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8228,6 +8277,7 @@
           <t>narrateur|Léa se souvient de Léa. Et de les cubes. Et de un morceau de pain. La lumière est claire. Léa sourit. Maman sourit aussi. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8395,6 +8445,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8562,6 +8613,7 @@
           <t>narrateur|Léa et son amie ont le livre. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute. Maman reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8753,6 +8805,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8920,6 +8973,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Léa s'arrête. Un panier est posé sur le banc. Léa dit merci à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9087,6 +9141,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9254,6 +9309,7 @@
           <t>narrateur|Léa range le livre. un yaourt reste près de Léa. On range un objet. Léa prend la main de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9421,6 +9477,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9588,6 +9645,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On se tient la main. Léa pose le livre à sa place. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9755,6 +9813,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9922,6 +9981,7 @@
           <t>narrateur|Léa et son amie ont la dînette. Léa dit son malaise. Elle a peur. Elle raconte à papa ou maman. Maman l'écoute. Maman montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10113,6 +10173,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10280,6 +10341,7 @@
           <t>narrateur|Léa rejoint une pomme. la dînette est rangé. Léa est fini. Une tasse cliquette. Léa tend une pomme à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10447,6 +10509,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10614,6 +10677,7 @@
           <t>narrateur|Près de un yaourt. Léa pose la dînette. Léa est derrière. Une cloche tinte, tout loin. Papa n'est pas loin. Léa les rejoint. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10781,6 +10845,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10948,6 +11013,7 @@
           <t>narrateur|Léa montre un morceau de pain. Maman a vu Léa. Et la dînette. On écoute jusqu'au bout. Léa enfile ses chaussons. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11115,6 +11181,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11349,7 @@
           <t>narrateur|Léa joue avec Sami. Un bruit étrange vient du bois. Léa a peur. Elle sent un malaise. Elle raconte à maman. Maman l'écoute. On raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11533,7 @@
           <t>narrateur|On garde le malaise, ou on raconte ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11705,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Léa hoche la tête. On continue, avec maman. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11827,6 +11897,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11994,6 +12065,7 @@
           <t>narrateur|Léa et Sami ont les cubes. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman. Maman reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12185,6 +12257,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12352,6 +12425,7 @@
           <t>narrateur|Léa a choisi Sami. Puis les cubes. Puis une pomme. Une pomme brille un peu. Léa caresse le doudou. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12519,6 +12593,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12686,6 +12761,7 @@
           <t>narrateur|Léa s'arrête près de un yaourt. les cubes est rangé. Ça sent le pain chaud. Léa serre la main de maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12853,6 +12929,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13020,6 +13097,7 @@
           <t>narrateur|Léa se souvient de Sami. Et de les cubes. Et de un morceau de pain. Un ruban reste dans la poche. Léa essuie ses mains. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13187,6 +13265,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13354,6 +13433,7 @@
           <t>narrateur|Léa et Sami ont le livre. Un bruit revient. Léa a peur. Elle sent un malaise. Elle raconte à papa ou maman. Maman montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13545,6 +13625,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13712,6 +13793,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Léa s'arrête. Une feuille tombe. Léa range Sami dans sa tête, comme un souvenir. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13879,6 +13961,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14046,6 +14129,7 @@
           <t>narrateur|Léa range le livre. un yaourt reste près de Sami. Un vélo passe au loin. Léa ferme le sac. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14213,6 +14297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14380,6 +14465,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. Les chaussures font toc toc. Léa répète tout bas le geste. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14547,6 +14633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14715,6 +14802,7 @@
 maman|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14906,6 +14994,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15073,6 +15162,7 @@
           <t>narrateur|Léa rejoint une pomme. la dînette est rangé. Sami est fini. La couverture est douce. Léa raccroche un linge. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15240,6 +15330,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15407,6 +15498,7 @@
           <t>narrateur|Près de un yaourt. Léa pose la dînette. Sami est derrière. Le sol est un peu froid. Léa boit une gorgée d'eau. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15574,6 +15666,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15741,6 +15834,7 @@
           <t>narrateur|Léa montre un morceau de pain. Maman a vu Sami. Et la dînette. Un galet est encore chaud. Léa ferme la porte, tout doux. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15908,6 +16002,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15926,7 +16021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15950,6 +16045,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16151,6 +16260,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
